--- a/productos12.xlsx
+++ b/productos12.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yunior\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yunior\Desktop\Nueva carpeta (4)\programa5\costousd\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -770,7 +770,7 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla26" displayName="Tabla26" ref="A1:E198" totalsRowShown="0">
   <autoFilter ref="A1:E198"/>
-  <sortState ref="A2:F198">
+  <sortState ref="A2:E198">
     <sortCondition ref="B1:B198"/>
   </sortState>
   <tableColumns count="5">
